--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.085924177769082</v>
+        <v>2.600358908108689</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.632026391026381</v>
+        <v>2.080688129181475</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.145019013502051</v>
+        <v>3.812924058938854</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>287174.9429296318</v>
+        <v>333610.8983716682</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.378528740348609</v>
+        <v>3.924834098490215</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>993.3333333333334</v>
+        <v>876.587090850407</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>557.3333333333334</v>
+        <v>440.587090850407</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.632026391026381</v>
+        <v>2.080688129181475</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.632026391026381</v>
+        <v>2.080688129181475</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.77771973886728</v>
+        <v>1.357729709991308</v>
       </c>
       <c r="F11" t="n">
-        <v>1.405680409807002</v>
+        <v>1.073585455243804</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.145019013502051</v>
+        <v>3.812924058938854</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.980504234514669</v>
+        <v>1.592052018786355</v>
       </c>
       <c r="C2" t="n">
-        <v>2.399891716505631</v>
+        <v>1.962882973811277</v>
       </c>
       <c r="D2" t="n">
-        <v>2.819279198496592</v>
+        <v>2.333713928836199</v>
       </c>
       <c r="E2" t="n">
-        <v>3.238666680487554</v>
+        <v>2.704544883861121</v>
       </c>
       <c r="F2" t="n">
-        <v>3.658054162478515</v>
+        <v>3.075375838886043</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.113826724150914</v>
+        <v>1.7253745084226</v>
       </c>
       <c r="C3" t="n">
-        <v>2.533214206141876</v>
+        <v>2.096205463447522</v>
       </c>
       <c r="D3" t="n">
-        <v>2.952601688132837</v>
+        <v>2.467036418472444</v>
       </c>
       <c r="E3" t="n">
-        <v>3.371989170123798</v>
+        <v>2.837867373497367</v>
       </c>
       <c r="F3" t="n">
-        <v>3.79137665211476</v>
+        <v>3.208698328522288</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.247149213787159</v>
+        <v>1.858696998058845</v>
       </c>
       <c r="C4" t="n">
-        <v>2.66653669577812</v>
+        <v>2.229527953083767</v>
       </c>
       <c r="D4" t="n">
-        <v>3.085924177769082</v>
+        <v>2.600358908108689</v>
       </c>
       <c r="E4" t="n">
-        <v>3.505311659760043</v>
+        <v>2.971189863133611</v>
       </c>
       <c r="F4" t="n">
-        <v>3.924699141751004</v>
+        <v>3.342020818158533</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.380471703423403</v>
+        <v>1.99201948769509</v>
       </c>
       <c r="C5" t="n">
-        <v>2.799859185414365</v>
+        <v>2.362850442720012</v>
       </c>
       <c r="D5" t="n">
-        <v>3.219246667405327</v>
+        <v>2.733681397744933</v>
       </c>
       <c r="E5" t="n">
-        <v>3.638634149396288</v>
+        <v>3.104512352769856</v>
       </c>
       <c r="F5" t="n">
-        <v>4.058021631387249</v>
+        <v>3.475343307794778</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.513794193059648</v>
+        <v>2.125341977331334</v>
       </c>
       <c r="C6" t="n">
-        <v>2.933181675050609</v>
+        <v>2.496172932356256</v>
       </c>
       <c r="D6" t="n">
-        <v>3.352569157041571</v>
+        <v>2.867003887381178</v>
       </c>
       <c r="E6" t="n">
-        <v>3.771956639032533</v>
+        <v>3.2378348424061</v>
       </c>
       <c r="F6" t="n">
-        <v>4.191344121023494</v>
+        <v>3.608665797431023</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.92</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.600358908108689</v>
+        <v>2.593785877506456</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.080688129181475</v>
+        <v>2.073224738585557</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.812924058938854</v>
+        <v>3.808428534988555</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>333610.8983716682</v>
+        <v>334239.4955453867</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.924834098490215</v>
+        <v>3.932229359357491</v>
       </c>
     </row>
   </sheetData>
@@ -612,7 +612,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>876.587090850407</v>
+        <v>875.0067129434933</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>440.587090850407</v>
+        <v>439.0067129434934</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.080688129181475</v>
+        <v>2.073224738585557</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.080688129181475</v>
+        <v>2.073224738585557</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.357729709991308</v>
+        <v>1.352044362449122</v>
       </c>
       <c r="F11" t="n">
-        <v>1.073585455243804</v>
+        <v>1.069089931293505</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.812924058938854</v>
+        <v>3.808428534988555</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.592052018786355</v>
+        <v>1.586793594304569</v>
       </c>
       <c r="C2" t="n">
-        <v>1.962882973811277</v>
+        <v>1.956967246269268</v>
       </c>
       <c r="D2" t="n">
-        <v>2.333713928836199</v>
+        <v>2.327140898233967</v>
       </c>
       <c r="E2" t="n">
-        <v>2.704544883861121</v>
+        <v>2.697314550198666</v>
       </c>
       <c r="F2" t="n">
-        <v>3.075375838886043</v>
+        <v>3.067488202163364</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.7253745084226</v>
+        <v>1.720116083940814</v>
       </c>
       <c r="C3" t="n">
-        <v>2.096205463447522</v>
+        <v>2.090289735905512</v>
       </c>
       <c r="D3" t="n">
-        <v>2.467036418472444</v>
+        <v>2.460463387870211</v>
       </c>
       <c r="E3" t="n">
-        <v>2.837867373497367</v>
+        <v>2.83063703983491</v>
       </c>
       <c r="F3" t="n">
-        <v>3.208698328522288</v>
+        <v>3.200810691799609</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.858696998058845</v>
+        <v>1.853438573577058</v>
       </c>
       <c r="C4" t="n">
-        <v>2.229527953083767</v>
+        <v>2.223612225541757</v>
       </c>
       <c r="D4" t="n">
-        <v>2.600358908108689</v>
+        <v>2.593785877506456</v>
       </c>
       <c r="E4" t="n">
-        <v>2.971189863133611</v>
+        <v>2.963959529471155</v>
       </c>
       <c r="F4" t="n">
-        <v>3.342020818158533</v>
+        <v>3.334133181435854</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.99201948769509</v>
+        <v>1.986761063213303</v>
       </c>
       <c r="C5" t="n">
-        <v>2.362850442720012</v>
+        <v>2.356934715178002</v>
       </c>
       <c r="D5" t="n">
-        <v>2.733681397744933</v>
+        <v>2.727108367142701</v>
       </c>
       <c r="E5" t="n">
-        <v>3.104512352769856</v>
+        <v>3.0972820191074</v>
       </c>
       <c r="F5" t="n">
-        <v>3.475343307794778</v>
+        <v>3.467455671072099</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.125341977331334</v>
+        <v>2.120083552849548</v>
       </c>
       <c r="C6" t="n">
-        <v>2.496172932356256</v>
+        <v>2.490257204814247</v>
       </c>
       <c r="D6" t="n">
-        <v>2.867003887381178</v>
+        <v>2.860430856778946</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2378348424061</v>
+        <v>3.230604508743645</v>
       </c>
       <c r="F6" t="n">
-        <v>3.608665797431023</v>
+        <v>3.600778160708343</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>334239.4955453867</v>
+        <v>332326.839993456</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.932229359357491</v>
+        <v>3.909727529334776</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.18</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>332326.839993456</v>
+        <v>339977.4622011791</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.909727529334776</v>
+        <v>3.999734849425637</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>339977.4622011791</v>
+        <v>329457.8566655598</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.999734849425637</v>
+        <v>3.875974784300704</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.15</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>329457.8566655598</v>
+        <v>396400.8009831379</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.875974784300704</v>
+        <v>4.663538835095739</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.593785877506456</v>
+        <v>2.512869737363784</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.808428534988555</v>
+        <v>3.538708067846315</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>396400.8009831379</v>
+        <v>404139.0362173724</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.663538835095739</v>
+        <v>4.754576896674969</v>
       </c>
     </row>
   </sheetData>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.352044362449122</v>
+        <v>1.010937383174155</v>
       </c>
       <c r="F11" t="n">
-        <v>1.069089931293505</v>
+        <v>0.7993694641512654</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.808428534988555</v>
+        <v>3.538708067846315</v>
       </c>
     </row>
     <row r="13">
@@ -1038,7 +1038,7 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.586793594304569</v>
+        <v>1.522060682190431</v>
       </c>
       <c r="C2" t="n">
-        <v>1.956967246269268</v>
+        <v>1.884142720140863</v>
       </c>
       <c r="D2" t="n">
-        <v>2.327140898233967</v>
+        <v>2.246224758091295</v>
       </c>
       <c r="E2" t="n">
-        <v>2.697314550198666</v>
+        <v>2.608306796041727</v>
       </c>
       <c r="F2" t="n">
-        <v>3.067488202163364</v>
+        <v>2.970388833992158</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.720116083940814</v>
+        <v>1.655383171826676</v>
       </c>
       <c r="C3" t="n">
-        <v>2.090289735905512</v>
+        <v>2.017465209777108</v>
       </c>
       <c r="D3" t="n">
-        <v>2.460463387870211</v>
+        <v>2.379547247727539</v>
       </c>
       <c r="E3" t="n">
-        <v>2.83063703983491</v>
+        <v>2.741629285677971</v>
       </c>
       <c r="F3" t="n">
-        <v>3.200810691799609</v>
+        <v>3.103711323628403</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.853438573577058</v>
+        <v>1.788705661462921</v>
       </c>
       <c r="C4" t="n">
-        <v>2.223612225541757</v>
+        <v>2.150787699413352</v>
       </c>
       <c r="D4" t="n">
-        <v>2.593785877506456</v>
+        <v>2.512869737363784</v>
       </c>
       <c r="E4" t="n">
-        <v>2.963959529471155</v>
+        <v>2.874951775314216</v>
       </c>
       <c r="F4" t="n">
-        <v>3.334133181435854</v>
+        <v>3.237033813264648</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.986761063213303</v>
+        <v>1.922028151099165</v>
       </c>
       <c r="C5" t="n">
-        <v>2.356934715178002</v>
+        <v>2.284110189049597</v>
       </c>
       <c r="D5" t="n">
-        <v>2.727108367142701</v>
+        <v>2.646192227000029</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0972820191074</v>
+        <v>3.008274264950461</v>
       </c>
       <c r="F5" t="n">
-        <v>3.467455671072099</v>
+        <v>3.370356302900892</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.120083552849548</v>
+        <v>2.05535064073541</v>
       </c>
       <c r="C6" t="n">
-        <v>2.490257204814247</v>
+        <v>2.417432678685842</v>
       </c>
       <c r="D6" t="n">
-        <v>2.860430856778946</v>
+        <v>2.779514716636274</v>
       </c>
       <c r="E6" t="n">
-        <v>3.230604508743645</v>
+        <v>3.141596754586705</v>
       </c>
       <c r="F6" t="n">
-        <v>3.600778160708343</v>
+        <v>3.503678792537137</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.85</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>404139.0362173724</v>
+        <v>397444.7417856146</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.754576896674969</v>
+        <v>4.675820491595466</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1240,35 +1239,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.512869737363784</v>
+        <v>3.093574677713323</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.073224738585557</v>
+        <v>2.793293771119508</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.538708067846315</v>
+        <v>3.794230126432226</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>397444.7417856146</v>
+        <v>387687.0624793071</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.675820491595466</v>
+        <v>4.561024264462436</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>875.0067129434933</v>
+        <v>807.5298079883261</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>81.12</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>53.569</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-395</v>
+        <v>-415.394</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-5</v>
+        <v>-0.343</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-153</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>439.0067129434934</v>
+        <v>591.4818079883261</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.073224738585557</v>
+        <v>2.793293771119508</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.073224738585557</v>
+        <v>2.793293771119508</v>
       </c>
     </row>
     <row r="13">
@@ -809,16 +809,16 @@
         <v>81500</v>
       </c>
       <c r="C2" t="n">
-        <v>71000</v>
+        <v>69781.25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4057969443051992</v>
+        <v>0.3469814507735449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4057969443051992</v>
+        <v>0.3469814507735449</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3953466177810275</v>
+        <v>0.3380457761478455</v>
       </c>
     </row>
     <row r="3">
@@ -831,16 +831,16 @@
         <v>99000</v>
       </c>
       <c r="C3" t="n">
-        <v>83600</v>
+        <v>81812.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4996618603267372</v>
+        <v>0.42665074677948</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4996618603267372</v>
+        <v>0.42665074677948</v>
       </c>
       <c r="F3" t="n">
-        <v>0.474258049901691</v>
+        <v>0.4049589676995182</v>
       </c>
     </row>
     <row r="4">
@@ -853,16 +853,16 @@
         <v>92000</v>
       </c>
       <c r="C4" t="n">
-        <v>78560</v>
+        <v>77000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.462115893918122</v>
+        <v>0.3947830283771059</v>
       </c>
       <c r="E4" t="n">
-        <v>0.462115893918122</v>
+        <v>0.3947830283771059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4273253644761562</v>
+        <v>0.3650616732956128</v>
       </c>
     </row>
     <row r="5">
@@ -875,16 +875,16 @@
         <v>67500</v>
       </c>
       <c r="C5" t="n">
-        <v>60920</v>
+        <v>60156.25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3307050114879687</v>
+        <v>0.2832460139687969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3307050114879687</v>
+        <v>0.2832460139687969</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2979324427819537</v>
+        <v>0.2551765891610783</v>
       </c>
     </row>
     <row r="6">
@@ -897,16 +897,16 @@
         <v>60000</v>
       </c>
       <c r="C6" t="n">
-        <v>55520</v>
+        <v>55000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.290477190335881</v>
+        <v>0.2491020299662533</v>
       </c>
       <c r="E6" t="n">
-        <v>0.290477190335881</v>
+        <v>0.2491020299662533</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2549519345463977</v>
+        <v>0.2186369413925238</v>
       </c>
     </row>
     <row r="7">
@@ -919,16 +919,16 @@
         <v>78000</v>
       </c>
       <c r="C7" t="n">
-        <v>68480</v>
+        <v>67375</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3870239611008915</v>
+        <v>0.3310475915723579</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3870239611008915</v>
+        <v>0.3310475915723579</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3309431416456894</v>
+        <v>0.2830778995635235</v>
       </c>
     </row>
     <row r="8">
@@ -941,16 +941,16 @@
         <v>81500</v>
       </c>
       <c r="C8" t="n">
-        <v>71000</v>
+        <v>69781.25</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4057969443051992</v>
+        <v>0.3469814507735449</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4057969443051992</v>
+        <v>0.3469814507735449</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3380598228473598</v>
+        <v>0.2890620282532315</v>
       </c>
     </row>
     <row r="9">
@@ -963,16 +963,16 @@
         <v>56500</v>
       </c>
       <c r="C9" t="n">
-        <v>53000</v>
+        <v>52593.75</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2717042071315734</v>
+        <v>0.2331681707650663</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2717042071315734</v>
+        <v>0.2331681707650663</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2205212297147743</v>
+        <v>0.1892445181114084</v>
       </c>
     </row>
     <row r="10">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.73933860369505</v>
+        <v>2.343264393624742</v>
       </c>
     </row>
     <row r="11">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.010937383174155</v>
+        <v>1.834990660491627</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7993694641512654</v>
+        <v>1.450965732807484</v>
       </c>
     </row>
     <row r="12">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.538708067846315</v>
+        <v>3.794230126432226</v>
       </c>
     </row>
     <row r="13">
@@ -1036,8 +1036,8 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.522060682190431</v>
+        <v>2.197889267340563</v>
       </c>
       <c r="C2" t="n">
-        <v>1.884142720140863</v>
+        <v>2.532572452002353</v>
       </c>
       <c r="D2" t="n">
-        <v>2.246224758091295</v>
+        <v>2.867255636664142</v>
       </c>
       <c r="E2" t="n">
-        <v>2.608306796041727</v>
+        <v>3.201938821325932</v>
       </c>
       <c r="F2" t="n">
-        <v>2.970388833992158</v>
+        <v>3.536622005987722</v>
       </c>
     </row>
     <row r="3">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.655383171826676</v>
+        <v>2.311048787865154</v>
       </c>
       <c r="C3" t="n">
-        <v>2.017465209777108</v>
+        <v>2.645731972526943</v>
       </c>
       <c r="D3" t="n">
-        <v>2.379547247727539</v>
+        <v>2.980415157188733</v>
       </c>
       <c r="E3" t="n">
-        <v>2.741629285677971</v>
+        <v>3.315098341850523</v>
       </c>
       <c r="F3" t="n">
-        <v>3.103711323628403</v>
+        <v>3.649781526512312</v>
       </c>
     </row>
     <row r="4">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.788705661462921</v>
+        <v>2.424208308389744</v>
       </c>
       <c r="C4" t="n">
-        <v>2.150787699413352</v>
+        <v>2.758891493051534</v>
       </c>
       <c r="D4" t="n">
-        <v>2.512869737363784</v>
+        <v>3.093574677713323</v>
       </c>
       <c r="E4" t="n">
-        <v>2.874951775314216</v>
+        <v>3.428257862375113</v>
       </c>
       <c r="F4" t="n">
-        <v>3.237033813264648</v>
+        <v>3.762941047036902</v>
       </c>
     </row>
     <row r="5">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.922028151099165</v>
+        <v>2.537367828914334</v>
       </c>
       <c r="C5" t="n">
-        <v>2.284110189049597</v>
+        <v>2.872051013576124</v>
       </c>
       <c r="D5" t="n">
-        <v>2.646192227000029</v>
+        <v>3.206734198237914</v>
       </c>
       <c r="E5" t="n">
-        <v>3.008274264950461</v>
+        <v>3.541417382899703</v>
       </c>
       <c r="F5" t="n">
-        <v>3.370356302900892</v>
+        <v>3.876100567561493</v>
       </c>
     </row>
     <row r="6">
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.05535064073541</v>
+        <v>2.650527349438924</v>
       </c>
       <c r="C6" t="n">
-        <v>2.417432678685842</v>
+        <v>2.985210534100714</v>
       </c>
       <c r="D6" t="n">
-        <v>2.779514716636274</v>
+        <v>3.319893718762504</v>
       </c>
       <c r="E6" t="n">
-        <v>3.141596754586705</v>
+        <v>3.654576903424294</v>
       </c>
       <c r="F6" t="n">
-        <v>3.503678792537137</v>
+        <v>3.989260088086083</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.49</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="3">
@@ -1225,7 +1225,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.51</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.51</v>
+        <v>3.09</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.78</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>387687.0624793071</v>
+        <v>360645.5905305545</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.561024264462436</v>
+        <v>4.242889300359465</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.54</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>360645.5905305545</v>
+        <v>362899.0465262838</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.242889300359465</v>
+        <v>4.269400547368045</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.56</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>362899.0465262838</v>
+        <v>391067.2464729011</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.269400547368045</v>
+        <v>4.600791134975307</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.81</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>391067.2464729011</v>
+        <v>401207.7984536833</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.600791134975307</v>
+        <v>4.720091746513921</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>401207.7984536833</v>
+        <v>431629.4543960299</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.720091746513921</v>
+        <v>5.077993581129764</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.17</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>431629.4543960299</v>
+        <v>422615.6304131125</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.077993581129764</v>
+        <v>4.971948593095441</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.09</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>422615.6304131125</v>
+        <v>445150.1903704062</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.971948593095441</v>
+        <v>5.237061063181249</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>445150.1903704062</v>
+        <v>418108.7184216537</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.237061063181249</v>
+        <v>4.918926099078279</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.093574677713323</v>
+        <v>3.138322936781033</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.793293771119508</v>
+        <v>2.845016518733961</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.794230126432226</v>
+        <v>3.822704578890868</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>418108.7184216537</v>
+        <v>413066.8067869245</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.918926099078279</v>
+        <v>4.859609491610877</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>807.5298079883261</v>
+        <v>818.4821340878682</v>
       </c>
     </row>
     <row r="3">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>591.4818079883261</v>
+        <v>602.4341340878682</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.793293771119508</v>
+        <v>2.845016518733961</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.793293771119508</v>
+        <v>2.845016518733961</v>
       </c>
     </row>
     <row r="13">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.834990660491627</v>
+        <v>1.871001403642067</v>
       </c>
       <c r="F11" t="n">
-        <v>1.450965732807484</v>
+        <v>1.479440185266126</v>
       </c>
     </row>
     <row r="12">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.794230126432226</v>
+        <v>3.822704578890868</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1036,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.197889267340563</v>
+        <v>2.233687874594731</v>
       </c>
       <c r="C2" t="n">
-        <v>2.532572452002353</v>
+        <v>2.572845885163292</v>
       </c>
       <c r="D2" t="n">
-        <v>2.867255636664142</v>
+        <v>2.912003895731852</v>
       </c>
       <c r="E2" t="n">
-        <v>3.201938821325932</v>
+        <v>3.251161906300414</v>
       </c>
       <c r="F2" t="n">
-        <v>3.536622005987722</v>
+        <v>3.590319916868973</v>
       </c>
     </row>
     <row r="3">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.311048787865154</v>
+        <v>2.346847395119322</v>
       </c>
       <c r="C3" t="n">
-        <v>2.645731972526943</v>
+        <v>2.686005405687882</v>
       </c>
       <c r="D3" t="n">
-        <v>2.980415157188733</v>
+        <v>3.025163416256443</v>
       </c>
       <c r="E3" t="n">
-        <v>3.315098341850523</v>
+        <v>3.364321426825004</v>
       </c>
       <c r="F3" t="n">
-        <v>3.649781526512312</v>
+        <v>3.703479437393564</v>
       </c>
     </row>
     <row r="4">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.424208308389744</v>
+        <v>2.460006915643913</v>
       </c>
       <c r="C4" t="n">
-        <v>2.758891493051534</v>
+        <v>2.799164926212472</v>
       </c>
       <c r="D4" t="n">
-        <v>3.093574677713323</v>
+        <v>3.138322936781033</v>
       </c>
       <c r="E4" t="n">
-        <v>3.428257862375113</v>
+        <v>3.477480947349595</v>
       </c>
       <c r="F4" t="n">
-        <v>3.762941047036902</v>
+        <v>3.816638957918154</v>
       </c>
     </row>
     <row r="5">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.537367828914334</v>
+        <v>2.573166436168503</v>
       </c>
       <c r="C5" t="n">
-        <v>2.872051013576124</v>
+        <v>2.912324446737063</v>
       </c>
       <c r="D5" t="n">
-        <v>3.206734198237914</v>
+        <v>3.251482457305623</v>
       </c>
       <c r="E5" t="n">
-        <v>3.541417382899703</v>
+        <v>3.590640467874185</v>
       </c>
       <c r="F5" t="n">
-        <v>3.876100567561493</v>
+        <v>3.929798478442744</v>
       </c>
     </row>
     <row r="6">
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.650527349438924</v>
+        <v>2.686325956693093</v>
       </c>
       <c r="C6" t="n">
-        <v>2.985210534100714</v>
+        <v>3.025483967261653</v>
       </c>
       <c r="D6" t="n">
-        <v>3.319893718762504</v>
+        <v>3.364641977830214</v>
       </c>
       <c r="E6" t="n">
-        <v>3.654576903424294</v>
+        <v>3.703799988398775</v>
       </c>
       <c r="F6" t="n">
-        <v>3.989260088086083</v>
+        <v>4.042957998967335</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="3">
@@ -1225,7 +1225,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.05</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>413066.8067869245</v>
+        <v>425460.8147634362</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.859609491610877</v>
+        <v>5.005421350158073</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.16</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>425460.8147634362</v>
+        <v>458135.9267015122</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.005421350158073</v>
+        <v>5.389834431782496</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.45</v>
+        <v>6.525</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>458135.9267015122</v>
+        <v>466586.3866854972</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.389834431782496</v>
+        <v>5.489251608064674</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.525</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>466586.3866854972</v>
+        <v>459262.6546993768</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.489251608064674</v>
+        <v>5.403090055286786</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.138322936781033</v>
+        <v>2.965320900310975</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.822704578890868</v>
+        <v>3.246031123990674</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61250</v>
+        <v>58050</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85000</v>
+        <v>88475</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.207445850001802</v>
+        <v>2.092118066818034</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>459262.6546993768</v>
+        <v>620285.3135429758</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.403090055286786</v>
+        <v>7.010854066606113</v>
       </c>
     </row>
   </sheetData>
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81500</v>
+        <v>118900</v>
       </c>
       <c r="C2" t="n">
-        <v>69781.25</v>
+        <v>95493.75</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3469814507735449</v>
+        <v>0.517246117666229</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3469814507735449</v>
+        <v>0.517246117666229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3380457761478455</v>
+        <v>0.5039256851227379</v>
       </c>
     </row>
     <row r="3">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>99000</v>
+        <v>118900</v>
       </c>
       <c r="C3" t="n">
-        <v>81812.5</v>
+        <v>95493.75</v>
       </c>
       <c r="D3" t="n">
-        <v>0.42665074677948</v>
+        <v>0.517246117666229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.42665074677948</v>
+        <v>0.517246117666229</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4049589676995182</v>
+        <v>0.4909482883548392</v>
       </c>
     </row>
     <row r="4">
@@ -850,19 +850,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>92000</v>
+        <v>58050</v>
       </c>
       <c r="C4" t="n">
-        <v>77000</v>
+        <v>53659.375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3947830283771059</v>
+        <v>0.240224594125592</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3947830283771059</v>
+        <v>0.240224594125592</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3650616732956128</v>
+        <v>0.2221392157073126</v>
       </c>
     </row>
     <row r="5">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67500</v>
+        <v>58050</v>
       </c>
       <c r="C5" t="n">
-        <v>60156.25</v>
+        <v>53659.375</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2832460139687969</v>
+        <v>0.240224594125592</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2832460139687969</v>
+        <v>0.240224594125592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2551765891610783</v>
+        <v>0.2164185532662991</v>
       </c>
     </row>
     <row r="6">
@@ -894,19 +894,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>60000</v>
+        <v>26950</v>
       </c>
       <c r="C6" t="n">
-        <v>55000</v>
+        <v>32278.125</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2491020299662533</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2491020299662533</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2186369413925238</v>
+        <v>0.08657713044633228</v>
       </c>
     </row>
     <row r="7">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78000</v>
+        <v>26950</v>
       </c>
       <c r="C7" t="n">
-        <v>67375</v>
+        <v>32278.125</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3310475915723579</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3310475915723579</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2830778995635235</v>
+        <v>0.08434754420772939</v>
       </c>
     </row>
     <row r="8">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81500</v>
+        <v>26950</v>
       </c>
       <c r="C8" t="n">
-        <v>69781.25</v>
+        <v>32278.125</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3469814507735449</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3469814507735449</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2890620282532315</v>
+        <v>0.0821753756124434</v>
       </c>
     </row>
     <row r="9">
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56500</v>
+        <v>26950</v>
       </c>
       <c r="C9" t="n">
-        <v>52593.75</v>
+        <v>32278.125</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2331681707650663</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2331681707650663</v>
+        <v>0.09864087379504451</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1892445181114084</v>
+        <v>0.08005914600685374</v>
       </c>
     </row>
     <row r="10">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.343264393624742</v>
+        <v>1.766590938724548</v>
       </c>
     </row>
     <row r="11">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.822704578890868</v>
+        <v>3.246031123990674</v>
       </c>
     </row>
     <row r="13">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85000</v>
+        <v>88475</v>
       </c>
     </row>
   </sheetData>
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.233687874594731</v>
+        <v>2.11258644906569</v>
       </c>
       <c r="C2" t="n">
-        <v>2.572845885163292</v>
+        <v>2.451744459634251</v>
       </c>
       <c r="D2" t="n">
-        <v>2.912003895731852</v>
+        <v>2.790902470202811</v>
       </c>
       <c r="E2" t="n">
-        <v>3.251161906300414</v>
+        <v>3.130060480771373</v>
       </c>
       <c r="F2" t="n">
-        <v>3.590319916868973</v>
+        <v>3.469218491339932</v>
       </c>
     </row>
     <row r="3">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.346847395119322</v>
+        <v>2.199795664119772</v>
       </c>
       <c r="C3" t="n">
-        <v>2.686005405687882</v>
+        <v>2.538953674688333</v>
       </c>
       <c r="D3" t="n">
-        <v>3.025163416256443</v>
+        <v>2.878111685256893</v>
       </c>
       <c r="E3" t="n">
-        <v>3.364321426825004</v>
+        <v>3.217269695825455</v>
       </c>
       <c r="F3" t="n">
-        <v>3.703479437393564</v>
+        <v>3.556427706394014</v>
       </c>
     </row>
     <row r="4">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.460006915643913</v>
+        <v>2.287004879173854</v>
       </c>
       <c r="C4" t="n">
-        <v>2.799164926212472</v>
+        <v>2.626162889742414</v>
       </c>
       <c r="D4" t="n">
-        <v>3.138322936781033</v>
+        <v>2.965320900310975</v>
       </c>
       <c r="E4" t="n">
-        <v>3.477480947349595</v>
+        <v>3.304478910879536</v>
       </c>
       <c r="F4" t="n">
-        <v>3.816638957918154</v>
+        <v>3.643636921448096</v>
       </c>
     </row>
     <row r="5">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.573166436168503</v>
+        <v>2.374214094227936</v>
       </c>
       <c r="C5" t="n">
-        <v>2.912324446737063</v>
+        <v>2.713372104796496</v>
       </c>
       <c r="D5" t="n">
-        <v>3.251482457305623</v>
+        <v>3.052530115365057</v>
       </c>
       <c r="E5" t="n">
-        <v>3.590640467874185</v>
+        <v>3.391688125933618</v>
       </c>
       <c r="F5" t="n">
-        <v>3.929798478442744</v>
+        <v>3.730846136502178</v>
       </c>
     </row>
     <row r="6">
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.686325956693093</v>
+        <v>2.461423309282017</v>
       </c>
       <c r="C6" t="n">
-        <v>3.025483967261653</v>
+        <v>2.800581319850577</v>
       </c>
       <c r="D6" t="n">
-        <v>3.364641977830214</v>
+        <v>3.139739330419138</v>
       </c>
       <c r="E6" t="n">
-        <v>3.703799988398775</v>
+        <v>3.478897340987699</v>
       </c>
       <c r="F6" t="n">
-        <v>4.042957998967335</v>
+        <v>3.818055351556259</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="3">
@@ -1225,7 +1225,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>3.13</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.46</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>620285.3135429758</v>
+        <v>617241.770497262</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.010854066606113</v>
+        <v>6.976454032181543</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.44</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>617241.770497262</v>
+        <v>658329.601614397</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.976454032181543</v>
+        <v>7.440854496913218</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.71</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>658329.601614397</v>
+        <v>687243.2605486772</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.440854496913218</v>
+        <v>7.76765482394662</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.9</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>687243.2605486772</v>
+        <v>667460.2307515381</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.76765482394662</v>
+        <v>7.544054600186923</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/nat_fv_report.xlsx
+++ b/outputs/nat_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.965320900310975</v>
+        <v>2.892160117737397</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.845016518733961</v>
+        <v>2.763283210450258</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.246031123990674</v>
+        <v>3.192872901407389</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>667460.2307515381</v>
+        <v>678593.6303025768</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.544054600186923</v>
+        <v>7.669891272139891</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>818.4821340878682</v>
+        <v>787.7660518696107</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.12</v>
+        <v>133.294</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53.569</v>
+        <v>44.911</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-415.394</v>
+        <v>-406.566</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.343</v>
+        <v>-0.278</v>
       </c>
     </row>
     <row r="7">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>602.4341340878682</v>
+        <v>585.1270518696107</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.845016518733961</v>
+        <v>2.763283210450258</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.845016518733961</v>
+        <v>2.763283210450258</v>
       </c>
     </row>
     <row r="13">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.871001403642067</v>
+        <v>1.803773873891987</v>
       </c>
       <c r="F11" t="n">
-        <v>1.479440185266126</v>
+        <v>1.426281962682842</v>
       </c>
     </row>
     <row r="12">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.246031123990674</v>
+        <v>3.192872901407389</v>
       </c>
     </row>
     <row r="13">
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.11258644906569</v>
+        <v>2.065927569594693</v>
       </c>
       <c r="C2" t="n">
-        <v>2.451744459634251</v>
+        <v>2.391834628611964</v>
       </c>
       <c r="D2" t="n">
-        <v>2.790902470202811</v>
+        <v>2.717741687629234</v>
       </c>
       <c r="E2" t="n">
-        <v>3.130060480771373</v>
+        <v>3.043648746646505</v>
       </c>
       <c r="F2" t="n">
-        <v>3.469218491339932</v>
+        <v>3.369555805663774</v>
       </c>
     </row>
     <row r="3">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.199795664119772</v>
+        <v>2.153136784648775</v>
       </c>
       <c r="C3" t="n">
-        <v>2.538953674688333</v>
+        <v>2.479043843666045</v>
       </c>
       <c r="D3" t="n">
-        <v>2.878111685256893</v>
+        <v>2.804950902683315</v>
       </c>
       <c r="E3" t="n">
-        <v>3.217269695825455</v>
+        <v>3.130857961700587</v>
       </c>
       <c r="F3" t="n">
-        <v>3.556427706394014</v>
+        <v>3.456765020717855</v>
       </c>
     </row>
     <row r="4">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.287004879173854</v>
+        <v>2.240345999702857</v>
       </c>
       <c r="C4" t="n">
-        <v>2.626162889742414</v>
+        <v>2.566253058720127</v>
       </c>
       <c r="D4" t="n">
-        <v>2.965320900310975</v>
+        <v>2.892160117737397</v>
       </c>
       <c r="E4" t="n">
-        <v>3.304478910879536</v>
+        <v>3.218067176754668</v>
       </c>
       <c r="F4" t="n">
-        <v>3.643636921448096</v>
+        <v>3.543974235771937</v>
       </c>
     </row>
     <row r="5">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.374214094227936</v>
+        <v>2.327555214756939</v>
       </c>
       <c r="C5" t="n">
-        <v>2.713372104796496</v>
+        <v>2.653462273774209</v>
       </c>
       <c r="D5" t="n">
-        <v>3.052530115365057</v>
+        <v>2.979369332791479</v>
       </c>
       <c r="E5" t="n">
-        <v>3.391688125933618</v>
+        <v>3.30527639180875</v>
       </c>
       <c r="F5" t="n">
-        <v>3.730846136502178</v>
+        <v>3.631183450826019</v>
       </c>
     </row>
     <row r="6">
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.461423309282017</v>
+        <v>2.41476442981102</v>
       </c>
       <c r="C6" t="n">
-        <v>2.800581319850577</v>
+        <v>2.740671488828291</v>
       </c>
       <c r="D6" t="n">
-        <v>3.139739330419138</v>
+        <v>3.066578547845561</v>
       </c>
       <c r="E6" t="n">
-        <v>3.478897340987699</v>
+        <v>3.392485606862832</v>
       </c>
       <c r="F6" t="n">
-        <v>3.818055351556259</v>
+        <v>3.7183926658801</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="3">
@@ -1225,7 +1225,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
     </row>
   </sheetData>
